--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3C8F23A-C5A2-4857-8F56-77289D005C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{F3C8F23A-C5A2-4857-8F56-77289D005C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86B99330-7C8E-4A3C-B071-C5C5329CE649}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61079B35-9105-4B6F-9203-5A4D156C4106}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{61079B35-9105-4B6F-9203-5A4D156C4106}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,16 +39,16 @@
     <t>Year</t>
   </si>
   <si>
-    <t>GR</t>
+    <t>Child_Dependency_Ratio</t>
   </si>
   <si>
-    <t>DR</t>
+    <t>Aged_Dependency_Ratio</t>
   </si>
   <si>
-    <t>ADR</t>
+    <t>Dependency_Ratio</t>
   </si>
   <si>
-    <t>CDR</t>
+    <t>Gender_Ratio</t>
   </si>
 </sst>
 </file>
@@ -56,9 +56,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0;\-0.0;0.0;@"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0;\-0.0;0.0;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -147,7 +147,7 @@
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -203,14 +203,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -572,7 +571,10 @@
   <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -580,16 +582,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -605,7 +607,7 @@
       <c r="D2" s="1">
         <v>63.22223798177987</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>102.2</v>
       </c>
     </row>
@@ -622,7 +624,7 @@
       <c r="D3" s="1">
         <v>63.246539984349639</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>102</v>
       </c>
     </row>
@@ -639,7 +641,7 @@
       <c r="D4" s="1">
         <v>62.914798070258712</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>101.7</v>
       </c>
     </row>
@@ -656,7 +658,7 @@
       <c r="D5" s="1">
         <v>62.519211032308675</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>101.6</v>
       </c>
     </row>
@@ -673,7 +675,7 @@
       <c r="D6" s="1">
         <v>62.142752703915896</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>101.5</v>
       </c>
     </row>
@@ -690,7 +692,7 @@
       <c r="D7" s="1">
         <v>61.694756421360516</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>101.4</v>
       </c>
     </row>
@@ -707,7 +709,7 @@
       <c r="D8" s="1">
         <v>61.203668818954483</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>101.3</v>
       </c>
     </row>
@@ -724,7 +726,7 @@
       <c r="D9" s="1">
         <v>60.621346915972133</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>101.2</v>
       </c>
     </row>
@@ -741,7 +743,7 @@
       <c r="D10" s="1">
         <v>59.996162969861324</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>101.2</v>
       </c>
     </row>
@@ -758,7 +760,7 @@
       <c r="D11" s="1">
         <v>59.51330426548175</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>101.1</v>
       </c>
     </row>
@@ -775,7 +777,7 @@
       <c r="D12" s="1">
         <v>59.144409522961226</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>101.1</v>
       </c>
     </row>
@@ -792,7 +794,7 @@
       <c r="D13" s="1">
         <v>58.787963143321697</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>101</v>
       </c>
     </row>
@@ -809,7 +811,7 @@
       <c r="D14" s="1">
         <v>58.438760779715416</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>100.9</v>
       </c>
     </row>
@@ -826,7 +828,7 @@
       <c r="D15" s="1">
         <v>57.979431266963154</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <v>100.8</v>
       </c>
     </row>
@@ -843,7 +845,7 @@
       <c r="D16" s="1">
         <v>57.364992406964241</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>100.8</v>
       </c>
     </row>
@@ -860,7 +862,7 @@
       <c r="D17" s="1">
         <v>56.692034995797634</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>100.5</v>
       </c>
     </row>
@@ -877,7 +879,7 @@
       <c r="D18" s="1">
         <v>55.969290288046928</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>100.3</v>
       </c>
     </row>
@@ -894,7 +896,7 @@
       <c r="D19" s="1">
         <v>55.225195220962398</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>100.1</v>
       </c>
     </row>
@@ -911,7 +913,7 @@
       <c r="D20" s="1">
         <v>54.547787371623244</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>99.9</v>
       </c>
     </row>
@@ -928,7 +930,7 @@
       <c r="D21" s="1">
         <v>53.97518871349348</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>99.8</v>
       </c>
     </row>
@@ -945,7 +947,7 @@
       <c r="D22" s="1">
         <v>53.522720516234259</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -962,7 +964,7 @@
       <c r="D23" s="1">
         <v>53.127055079121796</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -979,7 +981,7 @@
       <c r="D24" s="1">
         <v>52.70017159382536</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -996,7 +998,7 @@
       <c r="D25" s="1">
         <v>52.203948025423699</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -1013,7 +1015,7 @@
       <c r="D26" s="1">
         <v>51.652832266287085</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -1030,7 +1032,7 @@
       <c r="D27" s="1">
         <v>51.076359514440917</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -1047,7 +1049,7 @@
       <c r="D28" s="1">
         <v>50.505740102241688</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="2">
         <v>99.7</v>
       </c>
     </row>
@@ -1064,7 +1066,7 @@
       <c r="D29" s="1">
         <v>50.013789495374574</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="2">
         <v>99.6</v>
       </c>
     </row>
@@ -1081,7 +1083,7 @@
       <c r="D30" s="1">
         <v>49.676481279534713</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="2">
         <v>99.6</v>
       </c>
     </row>
@@ -1098,7 +1100,7 @@
       <c r="D31" s="1">
         <v>49.487625924250572</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="2">
         <v>99.5</v>
       </c>
     </row>
@@ -1115,7 +1117,7 @@
       <c r="D32" s="1">
         <v>49.468124287535467</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>99.4</v>
       </c>
     </row>
@@ -1132,7 +1134,7 @@
       <c r="D33" s="1">
         <v>49.61706801364452</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="2">
         <v>99.3</v>
       </c>
     </row>
@@ -1149,7 +1151,7 @@
       <c r="D34" s="1">
         <v>49.811919085308006</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="2">
         <v>99.2</v>
       </c>
     </row>
@@ -1166,7 +1168,7 @@
       <c r="D35" s="1">
         <v>49.986077126087487</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="2">
         <v>99.1</v>
       </c>
     </row>
@@ -1183,7 +1185,7 @@
       <c r="D36" s="1">
         <v>50.095036616999899</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2">
         <v>99.1</v>
       </c>
     </row>
@@ -1200,7 +1202,7 @@
       <c r="D37" s="1">
         <v>50.109195672057993</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="2">
         <v>99</v>
       </c>
     </row>
@@ -1217,7 +1219,7 @@
       <c r="D38" s="1">
         <v>50.0490001668879</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="2">
         <v>98.9</v>
       </c>
     </row>
@@ -1234,7 +1236,7 @@
       <c r="D39" s="1">
         <v>49.9340260684314</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="2">
         <v>98.7</v>
       </c>
     </row>
@@ -1251,7 +1253,7 @@
       <c r="D40" s="1">
         <v>49.79801208892475</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="2">
         <v>98.6</v>
       </c>
     </row>
@@ -1268,7 +1270,7 @@
       <c r="D41" s="1">
         <v>49.636719247448909</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1285,7 +1287,7 @@
       <c r="D42" s="1">
         <v>49.459837149996119</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1302,7 +1304,7 @@
       <c r="D43" s="1">
         <v>49.28683546190102</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1319,7 +1321,7 @@
       <c r="D44" s="1">
         <v>49.073927866430587</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1336,7 +1338,7 @@
       <c r="D45" s="1">
         <v>48.844561734412189</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="2">
         <v>98.6</v>
       </c>
     </row>
@@ -1353,7 +1355,7 @@
       <c r="D46" s="1">
         <v>48.649765067750202</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="2">
         <v>98.6</v>
       </c>
     </row>
@@ -1370,7 +1372,7 @@
       <c r="D47" s="1">
         <v>48.475299793367753</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="2">
         <v>98.7</v>
       </c>
     </row>
@@ -1387,7 +1389,7 @@
       <c r="D48" s="1">
         <v>48.329676399825118</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="2">
         <v>98.8</v>
       </c>
     </row>
@@ -1404,7 +1406,7 @@
       <c r="D49" s="1">
         <v>48.218323272123484</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="2">
         <v>98.9</v>
       </c>
     </row>
@@ -1421,7 +1423,7 @@
       <c r="D50" s="1">
         <v>48.12539032511647</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="2">
         <v>99.1</v>
       </c>
     </row>
@@ -1438,7 +1440,7 @@
       <c r="D51" s="1">
         <v>48.148257170966389</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="2">
         <v>99.1</v>
       </c>
     </row>
@@ -1455,7 +1457,7 @@
       <c r="D52" s="1">
         <v>48.363861110940888</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="2">
         <v>99.1</v>
       </c>
     </row>
@@ -1472,7 +1474,7 @@
       <c r="D53" s="1">
         <v>48.768238322988275</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="2">
         <v>99</v>
       </c>
     </row>
@@ -1489,7 +1491,7 @@
       <c r="D54" s="1">
         <v>49.328972689837791</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="2">
         <v>99</v>
       </c>
     </row>
@@ -1506,7 +1508,7 @@
       <c r="D55" s="1">
         <v>49.92436731239188</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="2">
         <v>98.9</v>
       </c>
     </row>
@@ -1523,7 +1525,7 @@
       <c r="D56" s="1">
         <v>50.491060899885241</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="2">
         <v>98.7</v>
       </c>
     </row>
@@ -1540,7 +1542,7 @@
       <c r="D57" s="1">
         <v>51.063301029401217</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1557,7 +1559,7 @@
       <c r="D58" s="1">
         <v>51.603445574586225</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1574,7 +1576,7 @@
       <c r="D59" s="1">
         <v>52.042421492171165</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1591,7 +1593,7 @@
       <c r="D60" s="1">
         <v>52.445515169280377</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1608,7 +1610,7 @@
       <c r="D61" s="1">
         <v>52.919758431589557</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1625,7 +1627,7 @@
       <c r="D62" s="1">
         <v>53.606124638161646</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="2">
         <v>98.5</v>
       </c>
     </row>
@@ -1642,7 +1644,7 @@
       <c r="D63" s="1">
         <v>54.255815759352529</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="3">
         <v>98.6</v>
       </c>
     </row>
@@ -1659,7 +1661,7 @@
       <c r="D64" s="1">
         <v>54.584771843465305</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="4">
         <v>98.5</v>
       </c>
     </row>
@@ -1676,7 +1678,7 @@
       <c r="D65" s="1">
         <v>54.833050159145735</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="5">
         <v>98.6</v>
       </c>
     </row>
@@ -1693,7 +1695,7 @@
       <c r="D66" s="1">
         <v>55.211692188951979</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="5">
         <v>98.6</v>
       </c>
     </row>
@@ -1701,16 +1703,16 @@
       <c r="A67">
         <v>2025</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67">
         <v>27.7</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67">
         <v>27.5</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67">
         <v>55.2</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67">
         <v>98.4</v>
       </c>
     </row>
